--- a/data/basis/samples_data.xlsx
+++ b/data/basis/samples_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyoma\Desktop\laboratory\ml\predict_activity\data\basis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9947CC2-F90B-4FF4-9E7C-1FCFDDA9ACD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C161573-95EC-4AD9-A4BB-EC6D86845E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-130" yWindow="0" windowWidth="14400" windowHeight="8180" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="フタル酸骨格" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
   <si>
     <t>化合物名</t>
     <rPh sb="0" eb="4">
@@ -481,14 +481,43 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3,6-ジフルオロフタル酸</t>
-    <rPh sb="12" eb="13">
-      <t>サン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>blank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>phthalic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>anthraquinone-2,3-dicarboxylic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maleic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4,5-difluorophthalic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3,6-difluorophthalic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4-nitrophthalic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-nitrophthalic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4-methoxyphthalic acid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-methoxyphtalic acid</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1699,31 +1728,31 @@
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>アントラキノン-2,3-ジカルボン酸</c:v>
+                  <c:v>anthraquinone-2,3-dicarboxylic acid</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>マレイン酸</c:v>
+                  <c:v>maleic acid</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4,5-ジフルオロフタル酸</c:v>
+                  <c:v>4,5-difluorophthalic acid</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3,6-ジフルオロフタル酸</c:v>
+                  <c:v>3,6-difluorophthalic acid</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4-ニトロフタル酸</c:v>
+                  <c:v>4-nitrophthalic acid</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3-ニトロフタル酸</c:v>
+                  <c:v>3-nitrophthalic acid</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4-メトキシフタル酸</c:v>
+                  <c:v>4-methoxyphthalic acid</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3-メトキシフタル酸</c:v>
+                  <c:v>3-methoxyphtalic acid</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>フタル酸</c:v>
+                  <c:v>phthalic acid</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>blank</c:v>
@@ -1817,9 +1846,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:ln w="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
+                  <a:noFill/>
                 </a:ln>
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
@@ -1855,9 +1882,7 @@
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:ln w="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1"/>
-                      </a:solidFill>
+                      <a:noFill/>
                     </a:ln>
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
@@ -1868,14 +1893,26 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:rPr lang="en-US" altLang="ja-JP">
+                    <a:ln w="0">
+                      <a:noFill/>
+                    </a:ln>
+                  </a:rPr>
                   <a:t>Yield</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
+                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0">
+                    <a:ln w="0">
+                      <a:noFill/>
+                    </a:ln>
+                  </a:rPr>
                   <a:t> of glucose (%)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US">
+                  <a:ln w="0">
+                    <a:noFill/>
+                  </a:ln>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1894,9 +1931,7 @@
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:ln w="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
+                    <a:noFill/>
                   </a:ln>
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
@@ -1906,7 +1941,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5871,7 +5906,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="B1">
         <v>17.7</v>
@@ -5879,7 +5914,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="B2">
         <v>18.7</v>
@@ -5887,7 +5922,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="B3">
         <v>14.9</v>
@@ -5895,7 +5930,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B4">
         <v>11.87</v>
@@ -5903,7 +5938,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="B5">
         <v>15.7</v>
@@ -5911,7 +5946,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="B6">
         <v>12.5</v>
@@ -5919,7 +5954,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="B7">
         <v>13.3</v>
@@ -5927,7 +5962,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -5935,7 +5970,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="B9">
         <v>13.3</v>
@@ -5943,7 +5978,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10">
         <v>0.7</v>
